--- a/FischerTropsch_Paper_Michi/Patagonien_FischerTropsch_1_Naphta_Greenfield_MH/Datenbank.xlsx
+++ b/FischerTropsch_Paper_Michi/Patagonien_FischerTropsch_1_Naphta_Greenfield_MH/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\FischerTropsch_Paper_Michi\FischerTropsch_Naphta_Greenfield_Patagonien_MH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\FischerTropsch_Paper_Michi\Patagonien_FischerTropsch_1_Naphta_Greenfield_MH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5948E1A-B4B8-4E25-B4B2-E902F4EDDAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC9A3F8-2854-46D7-9BEC-4D4BFF5F232B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-6885" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1730,9 +1730,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1742,10 +1739,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1754,8 +1754,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1769,17 +1778,8 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2277,22 +2277,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>69</v>
       </c>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="69" t="s">
         <v>70</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="70"/>
       <c r="B3" s="77"/>
       <c r="C3" t="s">
@@ -2349,7 +2349,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="70"/>
       <c r="B4" s="77"/>
       <c r="C4" t="s">
@@ -2365,7 +2365,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="70"/>
       <c r="B5" s="77"/>
       <c r="C5" t="s">
@@ -2381,7 +2381,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="70"/>
       <c r="B6" s="77"/>
       <c r="C6" t="s">
@@ -2397,7 +2397,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="70"/>
       <c r="B7" s="77"/>
       <c r="C7" t="s">
@@ -2413,7 +2413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="70"/>
       <c r="B8" s="80" t="s">
         <v>330</v>
@@ -2431,7 +2431,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="70"/>
       <c r="B9" s="81"/>
       <c r="C9" s="13" t="s">
@@ -2447,7 +2447,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="70"/>
       <c r="B10" s="81"/>
       <c r="C10" s="13" t="s">
@@ -2463,7 +2463,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="70"/>
       <c r="B11" s="81"/>
       <c r="C11" s="13" t="s">
@@ -2479,7 +2479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="70"/>
       <c r="B12" s="81"/>
       <c r="C12" s="13" t="s">
@@ -2495,7 +2495,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="70"/>
       <c r="B13" s="81"/>
       <c r="C13" s="13" t="s">
@@ -2511,7 +2511,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="70"/>
       <c r="B14" s="81"/>
       <c r="C14" s="13" t="s">
@@ -2527,7 +2527,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="70"/>
       <c r="B15" s="81"/>
       <c r="C15" s="13" t="s">
@@ -2543,7 +2543,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="70"/>
       <c r="B16" s="82"/>
       <c r="C16" s="36" t="s">
@@ -2559,7 +2559,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="70"/>
       <c r="B17" s="84" t="s">
         <v>262</v>
@@ -2577,7 +2577,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="70"/>
       <c r="B18" s="85"/>
       <c r="C18" s="13" t="s">
@@ -2593,7 +2593,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="70"/>
       <c r="B19" s="85"/>
       <c r="C19" s="13" t="s">
@@ -2609,7 +2609,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="70"/>
       <c r="B20" s="85"/>
       <c r="C20" s="13" t="s">
@@ -2625,7 +2625,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="70"/>
       <c r="B21" s="85"/>
       <c r="C21" s="13" t="s">
@@ -2641,7 +2641,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="70"/>
       <c r="B22" s="86"/>
       <c r="C22" s="36" t="s">
@@ -2657,7 +2657,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="70"/>
       <c r="B23" s="83" t="s">
         <v>229</v>
@@ -2675,7 +2675,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="70"/>
       <c r="B24" s="83"/>
       <c r="C24" s="44" t="s">
@@ -2691,7 +2691,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="70"/>
       <c r="B25" s="83"/>
       <c r="C25" s="44" t="s">
@@ -2707,7 +2707,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="70"/>
       <c r="B26" s="83"/>
       <c r="C26" s="44" t="s">
@@ -2723,7 +2723,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="70"/>
       <c r="B27" s="83"/>
       <c r="C27" s="44" t="s">
@@ -2739,7 +2739,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="70"/>
       <c r="B28" s="83"/>
       <c r="C28" s="44" t="s">
@@ -2755,7 +2755,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="69" t="s">
         <v>71</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="70"/>
       <c r="B30" s="73"/>
       <c r="C30" t="s">
@@ -2791,7 +2791,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="70"/>
       <c r="B31" s="73"/>
       <c r="C31" t="s">
@@ -2807,7 +2807,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="70"/>
       <c r="B32" s="73"/>
       <c r="C32" t="s">
@@ -2823,7 +2823,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="70"/>
       <c r="B33" s="73"/>
       <c r="C33" t="s">
@@ -2839,7 +2839,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="70"/>
       <c r="B34" s="73"/>
       <c r="C34" t="s">
@@ -2855,7 +2855,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="70"/>
       <c r="B35" s="73"/>
       <c r="C35" t="s">
@@ -2871,7 +2871,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="70"/>
       <c r="B36" s="74"/>
       <c r="C36" s="5" t="s">
@@ -2887,7 +2887,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="70"/>
       <c r="B37" s="75" t="s">
         <v>305</v>
@@ -2905,7 +2905,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="70"/>
       <c r="B38" s="73"/>
       <c r="C38" s="13" t="s">
@@ -2921,7 +2921,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="70"/>
       <c r="B39" s="73"/>
       <c r="C39" s="13" t="s">
@@ -2937,7 +2937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="70"/>
       <c r="B40" s="73"/>
       <c r="C40" s="13" t="s">
@@ -2953,7 +2953,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="70"/>
       <c r="B41" s="73"/>
       <c r="C41" s="13" t="s">
@@ -2969,7 +2969,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="70"/>
       <c r="B42" s="73"/>
       <c r="C42" s="13" t="s">
@@ -2985,7 +2985,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="70"/>
       <c r="B43" s="73"/>
       <c r="C43" s="13" t="s">
@@ -3001,7 +3001,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="70"/>
       <c r="B44" s="73"/>
       <c r="C44" s="36" t="s">
@@ -3017,7 +3017,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="70"/>
       <c r="B45" s="75" t="s">
         <v>201</v>
@@ -3035,7 +3035,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="70"/>
       <c r="B46" s="77"/>
       <c r="C46" t="s">
@@ -3052,7 +3052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="70"/>
       <c r="B47" s="77"/>
       <c r="C47" t="s">
@@ -3068,7 +3068,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="70"/>
       <c r="B48" s="77"/>
       <c r="C48" t="s">
@@ -3084,7 +3084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="70"/>
       <c r="B49" s="77"/>
       <c r="C49" t="s">
@@ -3100,7 +3100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="70"/>
       <c r="B50" s="77"/>
       <c r="C50" t="s">
@@ -3116,7 +3116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="70"/>
       <c r="B51" s="77"/>
       <c r="C51" t="s">
@@ -3132,7 +3132,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="70"/>
       <c r="B52" s="77"/>
       <c r="C52" t="s">
@@ -3148,7 +3148,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="70"/>
       <c r="B53" s="77"/>
       <c r="C53" t="s">
@@ -3164,7 +3164,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="71"/>
       <c r="B54" s="78"/>
       <c r="C54" s="15" t="s">
@@ -3180,7 +3180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="69" t="s">
         <v>72</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="70"/>
       <c r="B56" s="75" t="s">
         <v>4</v>
@@ -3218,7 +3218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="70"/>
       <c r="B57" s="73"/>
       <c r="C57" t="s">
@@ -3234,7 +3234,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="70"/>
       <c r="B58" s="73"/>
       <c r="C58" t="s">
@@ -3250,7 +3250,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="70"/>
       <c r="B59" s="73"/>
       <c r="C59" t="s">
@@ -3266,7 +3266,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="70"/>
       <c r="B60" s="73"/>
       <c r="C60" t="s">
@@ -3282,7 +3282,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="70"/>
       <c r="B61" s="73"/>
       <c r="C61" t="s">
@@ -3298,7 +3298,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="70"/>
       <c r="B62" s="74"/>
       <c r="C62" s="5" t="s">
@@ -3314,7 +3314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="70"/>
       <c r="B63" s="75" t="s">
         <v>5</v>
@@ -3332,7 +3332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="70"/>
       <c r="B64" s="73"/>
       <c r="C64" t="s">
@@ -3348,7 +3348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="70"/>
       <c r="B65" s="73"/>
       <c r="C65" t="s">
@@ -3364,7 +3364,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="70"/>
       <c r="B66" s="73"/>
       <c r="C66" t="s">
@@ -3380,7 +3380,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="70"/>
       <c r="B67" s="73"/>
       <c r="C67" t="s">
@@ -3396,7 +3396,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="70"/>
       <c r="B68" s="73"/>
       <c r="C68" t="s">
@@ -3412,7 +3412,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="71"/>
       <c r="B69" s="76"/>
       <c r="C69" s="15" t="s">
@@ -3428,7 +3428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="69" t="s">
         <v>76</v>
       </c>
@@ -3442,13 +3442,13 @@
         <v>78</v>
       </c>
       <c r="E70" s="58">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="57" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="70"/>
       <c r="B71" s="6" t="s">
         <v>288</v>
@@ -3460,13 +3460,13 @@
         <v>290</v>
       </c>
       <c r="E71" s="7">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F71" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="70"/>
       <c r="B72" s="17" t="s">
         <v>79</v>
@@ -3484,7 +3484,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="70"/>
       <c r="B73" s="17" t="s">
         <v>371</v>
@@ -3502,7 +3502,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="71"/>
       <c r="B74" s="61" t="s">
         <v>331</v>
@@ -3546,18 +3546,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F149"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="13" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="13" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="13"/>
+    <col min="1" max="1" width="14.54296875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" style="13" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="13" customWidth="1"/>
+    <col min="7" max="16384" width="11.54296875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="27" t="s">
         <v>69</v>
       </c>
@@ -3577,11 +3577,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="88" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="89" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -3595,8 +3595,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="89"/>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="88"/>
       <c r="B3" s="85"/>
       <c r="C3" s="13" t="s">
         <v>107</v>
@@ -3609,8 +3609,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="89"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="88"/>
       <c r="B4" s="85"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
@@ -3623,8 +3623,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="89"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="88"/>
       <c r="B5" s="85"/>
       <c r="C5" s="13" t="s">
         <v>138</v>
@@ -3637,8 +3637,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="89"/>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="88"/>
       <c r="B6" s="85"/>
       <c r="C6" s="13" t="s">
         <v>141</v>
@@ -3651,8 +3651,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="89"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="88"/>
       <c r="B7" s="85"/>
       <c r="C7" s="13" t="s">
         <v>155</v>
@@ -3665,8 +3665,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="89"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="88"/>
       <c r="B8" s="85"/>
       <c r="C8" s="13" t="s">
         <v>196</v>
@@ -3679,8 +3679,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="89"/>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="88"/>
       <c r="B9" s="85"/>
       <c r="C9" s="13" t="s">
         <v>167</v>
@@ -3693,8 +3693,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="89"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="88"/>
       <c r="B10" s="85"/>
       <c r="C10" s="13" t="s">
         <v>188</v>
@@ -3707,14 +3707,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="89"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="88"/>
       <c r="B11" s="85"/>
       <c r="E11" s="33"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="89"/>
-      <c r="B12" s="100" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="88"/>
+      <c r="B12" s="90" t="s">
         <v>364</v>
       </c>
       <c r="C12" s="35" t="s">
@@ -3728,8 +3728,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="89"/>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="88"/>
       <c r="B13" s="91"/>
       <c r="C13" s="13" t="s">
         <v>363</v>
@@ -3742,8 +3742,8 @@
         <v>358</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="89"/>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="88"/>
       <c r="B14" s="91"/>
       <c r="C14" s="13" t="s">
         <v>380</v>
@@ -3756,8 +3756,8 @@
         <v>377</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="89"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="88"/>
       <c r="B15" s="91"/>
       <c r="C15" s="13" t="s">
         <v>139</v>
@@ -3770,8 +3770,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="88"/>
       <c r="B16" s="91"/>
       <c r="C16" s="13" t="s">
         <v>238</v>
@@ -3784,8 +3784,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="89"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="88"/>
       <c r="B17" s="91"/>
       <c r="C17" s="13" t="s">
         <v>84</v>
@@ -3798,8 +3798,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="89"/>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="88"/>
       <c r="B18" s="91"/>
       <c r="C18" s="13" t="s">
         <v>141</v>
@@ -3812,8 +3812,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="89"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="88"/>
       <c r="B19" s="91"/>
       <c r="C19" s="13" t="s">
         <v>155</v>
@@ -3826,8 +3826,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="89"/>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="88"/>
       <c r="B20" s="91"/>
       <c r="C20" s="13" t="s">
         <v>196</v>
@@ -3840,8 +3840,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="88"/>
       <c r="B21" s="91"/>
       <c r="C21" s="13" t="s">
         <v>167</v>
@@ -3854,8 +3854,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="89"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="88"/>
       <c r="B22" s="91"/>
       <c r="C22" s="13" t="s">
         <v>188</v>
@@ -3868,16 +3868,16 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
-      <c r="B23" s="101"/>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="88"/>
+      <c r="B23" s="92"/>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
       <c r="E23" s="37"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="88"/>
       <c r="B24" s="84" t="s">
         <v>262</v>
       </c>
@@ -3892,8 +3892,8 @@
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="89"/>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="88"/>
       <c r="B25" s="85"/>
       <c r="C25" s="13" t="s">
         <v>107</v>
@@ -3906,8 +3906,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="89"/>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="88"/>
       <c r="B26" s="85"/>
       <c r="C26" s="13" t="s">
         <v>84</v>
@@ -3920,8 +3920,8 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="89"/>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="88"/>
       <c r="B27" s="85"/>
       <c r="C27" s="13" t="s">
         <v>283</v>
@@ -3934,8 +3934,8 @@
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="88"/>
       <c r="B28" s="85"/>
       <c r="C28" s="13" t="s">
         <v>141</v>
@@ -3948,8 +3948,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="89"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="88"/>
       <c r="B29" s="85"/>
       <c r="C29" s="13" t="s">
         <v>155</v>
@@ -3962,8 +3962,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="89"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="88"/>
       <c r="B30" s="85"/>
       <c r="C30" s="13" t="s">
         <v>196</v>
@@ -3976,8 +3976,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="89"/>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="88"/>
       <c r="B31" s="85"/>
       <c r="C31" s="13" t="s">
         <v>167</v>
@@ -3990,8 +3990,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="89"/>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="88"/>
       <c r="B32" s="85"/>
       <c r="C32" s="13" t="s">
         <v>188</v>
@@ -4004,16 +4004,16 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="89"/>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="88"/>
       <c r="B33" s="86"/>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
       <c r="E33" s="37"/>
       <c r="F33" s="36"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="89"/>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="88"/>
       <c r="B34" s="83" t="s">
         <v>229</v>
       </c>
@@ -4028,8 +4028,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="89"/>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="88"/>
       <c r="B35" s="83"/>
       <c r="C35" s="13" t="s">
         <v>107</v>
@@ -4042,8 +4042,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="89"/>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="88"/>
       <c r="B36" s="83"/>
       <c r="C36" s="13" t="s">
         <v>84</v>
@@ -4056,8 +4056,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="89"/>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="88"/>
       <c r="B37" s="83"/>
       <c r="C37" s="13" t="s">
         <v>270</v>
@@ -4070,8 +4070,8 @@
         <v>282</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="89"/>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="88"/>
       <c r="B38" s="83"/>
       <c r="C38" s="13" t="s">
         <v>248</v>
@@ -4084,8 +4084,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="89"/>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="88"/>
       <c r="B39" s="83"/>
       <c r="C39" s="13" t="s">
         <v>141</v>
@@ -4098,8 +4098,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="89"/>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="88"/>
       <c r="B40" s="83"/>
       <c r="C40" s="13" t="s">
         <v>155</v>
@@ -4112,8 +4112,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="89"/>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="88"/>
       <c r="B41" s="83"/>
       <c r="C41" s="13" t="s">
         <v>196</v>
@@ -4126,8 +4126,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="89"/>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="88"/>
       <c r="B42" s="83"/>
       <c r="C42" s="13" t="s">
         <v>167</v>
@@ -4140,8 +4140,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="89"/>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="88"/>
       <c r="B43" s="83"/>
       <c r="C43" s="13" t="s">
         <v>188</v>
@@ -4154,16 +4154,16 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="89"/>
+    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="88"/>
       <c r="B44" s="83"/>
       <c r="E44" s="33"/>
     </row>
-    <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="88" t="s">
+    <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="87" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="103" t="s">
+      <c r="B45" s="96" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="26" t="s">
@@ -4177,8 +4177,8 @@
         <v>392</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="89"/>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="88"/>
       <c r="B46" s="83"/>
       <c r="C46" s="13" t="s">
         <v>111</v>
@@ -4191,8 +4191,8 @@
         <v>393</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="89"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="88"/>
       <c r="B47" s="83"/>
       <c r="C47" s="13" t="s">
         <v>135</v>
@@ -4205,8 +4205,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="89"/>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="88"/>
       <c r="B48" s="83"/>
       <c r="C48" s="13" t="s">
         <v>136</v>
@@ -4219,8 +4219,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="89"/>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="88"/>
       <c r="B49" s="83"/>
       <c r="C49" s="13" t="s">
         <v>141</v>
@@ -4233,8 +4233,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="89"/>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="88"/>
       <c r="B50" s="83"/>
       <c r="C50" s="13" t="s">
         <v>155</v>
@@ -4247,8 +4247,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="89"/>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="88"/>
       <c r="B51" s="83"/>
       <c r="C51" s="13" t="s">
         <v>196</v>
@@ -4261,8 +4261,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="89"/>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="88"/>
       <c r="B52" s="83"/>
       <c r="C52" s="13" t="s">
         <v>167</v>
@@ -4275,8 +4275,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="89"/>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="88"/>
       <c r="B53" s="83"/>
       <c r="C53" s="13" t="s">
         <v>188</v>
@@ -4289,16 +4289,16 @@
         <v>149</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="89"/>
-      <c r="B54" s="95"/>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="88"/>
+      <c r="B54" s="97"/>
       <c r="C54" s="36"/>
       <c r="D54" s="36"/>
       <c r="E54" s="37"/>
       <c r="F54" s="36"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="89"/>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="88"/>
       <c r="B55" s="83" t="s">
         <v>305</v>
       </c>
@@ -4313,8 +4313,8 @@
         <v>328</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="89"/>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="88"/>
       <c r="B56" s="83"/>
       <c r="C56" s="13" t="s">
         <v>111</v>
@@ -4327,8 +4327,8 @@
         <v>329</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="89"/>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="88"/>
       <c r="B57" s="83"/>
       <c r="C57" s="13" t="s">
         <v>135</v>
@@ -4341,8 +4341,8 @@
         <v>391</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="89"/>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="88"/>
       <c r="B58" s="83"/>
       <c r="C58" s="13" t="s">
         <v>136</v>
@@ -4355,8 +4355,8 @@
         <v>391</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="89"/>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="88"/>
       <c r="B59" s="83"/>
       <c r="C59" s="13" t="s">
         <v>141</v>
@@ -4369,8 +4369,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="89"/>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="88"/>
       <c r="B60" s="83"/>
       <c r="C60" s="13" t="s">
         <v>155</v>
@@ -4383,8 +4383,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="89"/>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="88"/>
       <c r="B61" s="83"/>
       <c r="C61" s="13" t="s">
         <v>196</v>
@@ -4397,8 +4397,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="89"/>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="88"/>
       <c r="B62" s="83"/>
       <c r="C62" s="13" t="s">
         <v>167</v>
@@ -4411,8 +4411,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="89"/>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="88"/>
       <c r="B63" s="83"/>
       <c r="C63" s="13" t="s">
         <v>188</v>
@@ -4425,13 +4425,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="89"/>
-      <c r="B64" s="95"/>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="88"/>
+      <c r="B64" s="97"/>
       <c r="E64" s="33"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="89"/>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="88"/>
       <c r="B65" s="94" t="s">
         <v>6</v>
       </c>
@@ -4446,8 +4446,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="89"/>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="88"/>
       <c r="B66" s="83"/>
       <c r="C66" s="13" t="s">
         <v>113</v>
@@ -4460,8 +4460,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="89"/>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="88"/>
       <c r="B67" s="85"/>
       <c r="C67" s="13" t="s">
         <v>111</v>
@@ -4474,8 +4474,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="89"/>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="88"/>
       <c r="B68" s="85"/>
       <c r="C68" s="13" t="s">
         <v>107</v>
@@ -4488,8 +4488,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="89"/>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="88"/>
       <c r="B69" s="85"/>
       <c r="C69" s="13" t="s">
         <v>126</v>
@@ -4502,8 +4502,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="89"/>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="88"/>
       <c r="B70" s="85"/>
       <c r="C70" s="13" t="s">
         <v>127</v>
@@ -4516,8 +4516,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="89"/>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="88"/>
       <c r="B71" s="85"/>
       <c r="C71" s="13" t="s">
         <v>141</v>
@@ -4530,8 +4530,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="89"/>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="88"/>
       <c r="B72" s="85"/>
       <c r="C72" s="13" t="s">
         <v>155</v>
@@ -4544,8 +4544,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="89"/>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="88"/>
       <c r="B73" s="85"/>
       <c r="C73" s="13" t="s">
         <v>196</v>
@@ -4558,8 +4558,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="89"/>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="88"/>
       <c r="B74" s="85"/>
       <c r="C74" s="13" t="s">
         <v>167</v>
@@ -4572,8 +4572,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="89"/>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="88"/>
       <c r="B75" s="85"/>
       <c r="C75" s="13" t="s">
         <v>188</v>
@@ -4586,19 +4586,19 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="93"/>
-      <c r="B76" s="102"/>
+      <c r="B76" s="95"/>
       <c r="C76" s="40"/>
       <c r="D76" s="40"/>
       <c r="E76" s="41"/>
       <c r="F76" s="40"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="88" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="90" t="s">
+      <c r="B77" s="89" t="s">
         <v>73</v>
       </c>
       <c r="C77" s="26" t="s">
@@ -4612,8 +4612,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="89"/>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="88"/>
       <c r="B78" s="85"/>
       <c r="C78" s="13" t="s">
         <v>153</v>
@@ -4626,13 +4626,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="89"/>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="88"/>
       <c r="B79" s="86"/>
       <c r="E79" s="31"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="89"/>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="88"/>
       <c r="B80" s="94" t="s">
         <v>4</v>
       </c>
@@ -4647,8 +4647,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="89"/>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="88"/>
       <c r="B81" s="83"/>
       <c r="C81" s="13" t="s">
         <v>107</v>
@@ -4661,8 +4661,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="89"/>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="88"/>
       <c r="B82" s="83"/>
       <c r="C82" s="13" t="s">
         <v>122</v>
@@ -4675,8 +4675,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="89"/>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="88"/>
       <c r="B83" s="83"/>
       <c r="C83" s="13" t="s">
         <v>141</v>
@@ -4689,8 +4689,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="89"/>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="88"/>
       <c r="B84" s="83"/>
       <c r="C84" s="13" t="s">
         <v>155</v>
@@ -4703,8 +4703,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="89"/>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="88"/>
       <c r="B85" s="83"/>
       <c r="C85" s="13" t="s">
         <v>161</v>
@@ -4717,8 +4717,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="89"/>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="88"/>
       <c r="B86" s="83"/>
       <c r="C86" s="13" t="s">
         <v>196</v>
@@ -4731,8 +4731,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="89"/>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="88"/>
       <c r="B87" s="83"/>
       <c r="C87" s="13" t="s">
         <v>167</v>
@@ -4745,8 +4745,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="89"/>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="88"/>
       <c r="B88" s="83"/>
       <c r="C88" s="13" t="s">
         <v>188</v>
@@ -4759,12 +4759,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="89"/>
-      <c r="B89" s="95"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="89"/>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="88"/>
+      <c r="B89" s="97"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="88"/>
       <c r="B90" s="94" t="s">
         <v>5</v>
       </c>
@@ -4779,8 +4779,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="89"/>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="88"/>
       <c r="B91" s="83"/>
       <c r="C91" s="13" t="s">
         <v>108</v>
@@ -4793,8 +4793,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="89"/>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="88"/>
       <c r="B92" s="83"/>
       <c r="C92" s="13" t="s">
         <v>120</v>
@@ -4807,8 +4807,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="89"/>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="88"/>
       <c r="B93" s="83"/>
       <c r="C93" s="13" t="s">
         <v>141</v>
@@ -4821,8 +4821,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="89"/>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="88"/>
       <c r="B94" s="83"/>
       <c r="C94" s="13" t="s">
         <v>155</v>
@@ -4835,8 +4835,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="89"/>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="88"/>
       <c r="B95" s="83"/>
       <c r="C95" s="13" t="s">
         <v>161</v>
@@ -4849,8 +4849,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="89"/>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="88"/>
       <c r="B96" s="83"/>
       <c r="C96" s="13" t="s">
         <v>196</v>
@@ -4863,8 +4863,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="89"/>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="88"/>
       <c r="B97" s="83"/>
       <c r="C97" s="13" t="s">
         <v>167</v>
@@ -4877,8 +4877,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="89"/>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="88"/>
       <c r="B98" s="83"/>
       <c r="C98" s="13" t="s">
         <v>188</v>
@@ -4891,15 +4891,15 @@
         <v>149</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="93"/>
-      <c r="B99" s="96"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="88" t="s">
+      <c r="B99" s="99"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="B100" s="90" t="s">
+      <c r="B100" s="89" t="s">
         <v>73</v>
       </c>
       <c r="C100" s="26" t="s">
@@ -4913,8 +4913,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="89"/>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="88"/>
       <c r="B101" s="85"/>
       <c r="C101" s="13" t="s">
         <v>228</v>
@@ -4927,8 +4927,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="89"/>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="88"/>
       <c r="B102" s="85"/>
       <c r="C102" s="13" t="s">
         <v>150</v>
@@ -4941,16 +4941,16 @@
         <v>149</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="89"/>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="88"/>
       <c r="B103" s="86"/>
       <c r="C103" s="36"/>
       <c r="D103" s="36"/>
       <c r="E103" s="37"/>
       <c r="F103" s="36"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="89"/>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="88"/>
       <c r="B104" s="84" t="s">
         <v>292</v>
       </c>
@@ -4965,8 +4965,8 @@
         <v>282</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="89"/>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="88"/>
       <c r="B105" s="85"/>
       <c r="C105" s="13" t="s">
         <v>297</v>
@@ -4979,8 +4979,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="89"/>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="88"/>
       <c r="B106" s="85"/>
       <c r="C106" s="13" t="s">
         <v>298</v>
@@ -4993,13 +4993,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="89"/>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="88"/>
       <c r="B107" s="86"/>
       <c r="E107" s="33"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="89"/>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="88"/>
       <c r="B108" s="84" t="s">
         <v>79</v>
       </c>
@@ -5014,8 +5014,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="89"/>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="88"/>
       <c r="B109" s="85"/>
       <c r="C109" s="13" t="s">
         <v>151</v>
@@ -5028,17 +5028,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="89"/>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="88"/>
       <c r="B110" s="86"/>
       <c r="C110" s="36"/>
       <c r="D110" s="36"/>
       <c r="E110" s="37"/>
       <c r="F110" s="36"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="89"/>
-      <c r="B111" s="97" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="88"/>
+      <c r="B111" s="100" t="s">
         <v>371</v>
       </c>
       <c r="C111" s="35" t="s">
@@ -5052,9 +5052,9 @@
         <v>377</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="89"/>
-      <c r="B112" s="98"/>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="88"/>
+      <c r="B112" s="101"/>
       <c r="C112" s="13" t="s">
         <v>376</v>
       </c>
@@ -5066,16 +5066,16 @@
         <v>149</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="89"/>
-      <c r="B113" s="99"/>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="88"/>
+      <c r="B113" s="102"/>
       <c r="C113" s="36"/>
       <c r="D113" s="36"/>
       <c r="E113" s="37"/>
       <c r="F113" s="36"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="89"/>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="88"/>
       <c r="B114" s="91" t="s">
         <v>331</v>
       </c>
@@ -5090,8 +5090,8 @@
         <v>358</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="89"/>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="88"/>
       <c r="B115" s="91"/>
       <c r="C115" s="13" t="s">
         <v>362</v>
@@ -5104,19 +5104,19 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="93"/>
-      <c r="B116" s="92"/>
+      <c r="B116" s="98"/>
       <c r="C116" s="40"/>
       <c r="D116" s="40"/>
       <c r="E116" s="41"/>
       <c r="F116" s="40"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="88" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="87" t="s">
         <v>163</v>
       </c>
-      <c r="B117" s="90" t="s">
+      <c r="B117" s="89" t="s">
         <v>13</v>
       </c>
       <c r="C117" s="26" t="s">
@@ -5130,8 +5130,8 @@
         <v>140</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="89"/>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="88"/>
       <c r="B118" s="85"/>
       <c r="C118" s="13" t="s">
         <v>174</v>
@@ -5143,16 +5143,16 @@
         <v>140</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="89"/>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="88"/>
       <c r="B119" s="86"/>
       <c r="C119" s="36"/>
       <c r="D119" s="36"/>
       <c r="E119" s="36"/>
       <c r="F119" s="36"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="89"/>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="88"/>
       <c r="B120" s="84" t="s">
         <v>183</v>
       </c>
@@ -5166,8 +5166,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="89"/>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="88"/>
       <c r="B121" s="85"/>
       <c r="C121" s="13" t="s">
         <v>181</v>
@@ -5179,8 +5179,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="89"/>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="88"/>
       <c r="B122" s="85"/>
       <c r="C122" s="13" t="s">
         <v>177</v>
@@ -5192,8 +5192,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="89"/>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="88"/>
       <c r="B123" s="85"/>
       <c r="C123" s="13" t="s">
         <v>179</v>
@@ -5205,8 +5205,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="89"/>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="88"/>
       <c r="B124" s="85"/>
       <c r="C124" s="13" t="s">
         <v>182</v>
@@ -5218,8 +5218,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="89"/>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="88"/>
       <c r="B125" s="85"/>
       <c r="C125" s="13" t="s">
         <v>191</v>
@@ -5231,12 +5231,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="89"/>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="88"/>
       <c r="B126" s="86"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="89"/>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="88"/>
       <c r="B127" s="84" t="s">
         <v>206</v>
       </c>
@@ -5251,8 +5251,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="89"/>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="88"/>
       <c r="B128" s="85"/>
       <c r="C128" s="13" t="s">
         <v>204</v>
@@ -5264,8 +5264,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="89"/>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="88"/>
       <c r="B129" s="85"/>
       <c r="C129" s="13" t="s">
         <v>215</v>
@@ -5277,8 +5277,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="89"/>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="88"/>
       <c r="B130" s="85"/>
       <c r="C130" s="13" t="s">
         <v>205</v>
@@ -5290,8 +5290,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="89"/>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="88"/>
       <c r="B131" s="85"/>
       <c r="C131" s="13" t="s">
         <v>300</v>
@@ -5303,8 +5303,8 @@
         <v>304</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="89"/>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="88"/>
       <c r="B132" s="85"/>
       <c r="C132" s="44" t="s">
         <v>324</v>
@@ -5317,8 +5317,8 @@
         <v>304</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="89"/>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="88"/>
       <c r="B133" s="85"/>
       <c r="C133" s="44" t="s">
         <v>326</v>
@@ -5331,8 +5331,8 @@
         <v>304</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="89"/>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="88"/>
       <c r="B134" s="85"/>
       <c r="C134" s="13" t="s">
         <v>217</v>
@@ -5344,8 +5344,8 @@
         <v>218</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="89"/>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="88"/>
       <c r="B135" s="85"/>
       <c r="C135" s="13" t="s">
         <v>221</v>
@@ -5357,8 +5357,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="89"/>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="88"/>
       <c r="B136" s="85"/>
       <c r="C136" s="13" t="s">
         <v>202</v>
@@ -5370,8 +5370,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="89"/>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="88"/>
       <c r="B137" s="85"/>
       <c r="C137" s="44" t="s">
         <v>249</v>
@@ -5384,8 +5384,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="89"/>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="88"/>
       <c r="B138" s="85"/>
       <c r="C138" s="44" t="s">
         <v>383</v>
@@ -5398,8 +5398,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="89"/>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="88"/>
       <c r="B139" s="85"/>
       <c r="C139" s="44" t="s">
         <v>365</v>
@@ -5412,8 +5412,8 @@
         <v>213</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="89"/>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140" s="88"/>
       <c r="B140" s="85"/>
       <c r="C140" s="44" t="s">
         <v>385</v>
@@ -5426,16 +5426,16 @@
         <v>213</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="89"/>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="88"/>
       <c r="B141" s="86"/>
       <c r="C141" s="44"/>
       <c r="D141" s="44"/>
       <c r="E141" s="44"/>
       <c r="F141" s="44"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="89"/>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="88"/>
       <c r="B142" s="84" t="s">
         <v>222</v>
       </c>
@@ -5450,8 +5450,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="89"/>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="88"/>
       <c r="B143" s="85"/>
       <c r="C143" s="13" t="s">
         <v>302</v>
@@ -5463,8 +5463,8 @@
         <v>304</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="89"/>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="88"/>
       <c r="B144" s="85"/>
       <c r="C144" s="13" t="s">
         <v>225</v>
@@ -5476,8 +5476,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="89"/>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" s="88"/>
       <c r="B145" s="85"/>
       <c r="C145" s="44" t="s">
         <v>251</v>
@@ -5490,8 +5490,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="89"/>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" s="88"/>
       <c r="B146" s="85"/>
       <c r="C146" s="44" t="s">
         <v>366</v>
@@ -5504,17 +5504,17 @@
         <v>213</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="89"/>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" s="88"/>
       <c r="B147" s="86"/>
       <c r="C147" s="36"/>
       <c r="D147" s="36"/>
       <c r="E147" s="36"/>
       <c r="F147" s="36"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="89"/>
-      <c r="B148" s="87" t="s">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" s="88"/>
+      <c r="B148" s="103" t="s">
         <v>386</v>
       </c>
       <c r="C148" s="13" t="s">
@@ -5527,9 +5527,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="89"/>
-      <c r="B149" s="87"/>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" s="88"/>
+      <c r="B149" s="103"/>
       <c r="C149" s="13" t="s">
         <v>388</v>
       </c>
@@ -5542,15 +5542,12 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A2:A44"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="B34:B44"/>
-    <mergeCell ref="A45:A76"/>
-    <mergeCell ref="B65:B76"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B45:B54"/>
-    <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A117:A149"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B127:B141"/>
+    <mergeCell ref="B120:B126"/>
     <mergeCell ref="B114:B116"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A77:A99"/>
@@ -5561,12 +5558,15 @@
     <mergeCell ref="B104:B107"/>
     <mergeCell ref="B108:B110"/>
     <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A117:A149"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="B120:B126"/>
+    <mergeCell ref="A2:A44"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="B34:B44"/>
+    <mergeCell ref="A45:A76"/>
+    <mergeCell ref="B65:B76"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B45:B54"/>
+    <mergeCell ref="B55:B64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5576,57 +5576,57 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C614C4-2B7C-4798-B4E2-788104541F45}">
   <dimension ref="B1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.5546875" style="49"/>
+    <col min="2" max="2" width="11.54296875" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B1" s="49" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="49" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B22" s="52" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="49" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" s="49" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B27" s="49" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" s="49" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" s="50" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B30" s="51" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B31" s="51"/>
     </row>
   </sheetData>
